--- a/data/trans_orig/IP1021_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1021_2023-Estudios-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52255</t>
+          <t>52405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56010</t>
+          <t>55222</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109963</t>
+          <t>109731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116300</t>
+          <t>116291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>444753</t>
+          <t>444901</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>454615</t>
+          <t>454346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504865</t>
+          <t>504473</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>513980</t>
+          <t>514007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>954040</t>
+          <t>954308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>966986</t>
+          <t>966904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15691</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141430</t>
+          <t>141517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148028</t>
+          <t>148063</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171178</t>
+          <t>171402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181281</t>
+          <t>181106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316674</t>
+          <t>317252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>327401</t>
+          <t>328011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20644</t>
+          <t>19738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>17572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35425</t>
+          <t>35623</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>643279</t>
+          <t>644185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>655630</t>
+          <t>655393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>740350</t>
+          <t>740660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754323</t>
+          <t>754091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1389934</t>
+          <t>1389736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1407201</t>
+          <t>1407787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1021_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1021_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5855</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2273</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6782</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>341</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55195</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50877</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>54287</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52405</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>46418</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>44666</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60189</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55222</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62004</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>149</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>114475</t>
+          <t>101613</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>97127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116291</t>
+          <t>103149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2422</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11969</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8963</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5348</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14793</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22005</t>
+          <t>21732</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>470240</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>463709</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>473256</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>450731</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>444901</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>454346</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>510617</t>
+          <t>422439</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504473</t>
+          <t>416677</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514007</t>
+          <t>426265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>961348</t>
+          <t>892679</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>954308</t>
+          <t>885548</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>966904</t>
+          <t>897990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4288</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1641</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9829</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3730</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1488</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8034</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7410</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4926</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11411</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15113</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163574</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>158033</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166221</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>145821</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>141517</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148063</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>146243</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>142566</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148570</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,51%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>177887</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>171402</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>181106</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>323709</t>
+          <t>309818</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317252</t>
+          <t>303453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328011</t>
+          <t>313754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167862</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167862</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167862</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182813</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182813</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182813</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332365</t>
+          <t>317839</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332365</t>
+          <t>317839</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332365</t>
+          <t>317839</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11263</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19304</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>13084</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8530</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19738</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35623</t>
+          <t>34672</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>689010</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>680969</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>693607</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>919</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>650839</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>644185</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>655393</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>748693</t>
+          <t>615100</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>740660</t>
+          <t>607854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754091</t>
+          <t>620037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1399532</t>
+          <t>1304109</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1389736</t>
+          <t>1293937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1407787</t>
+          <t>1311754</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425359</t>
+          <t>1328609</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425359</t>
+          <t>1328609</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425359</t>
+          <t>1328609</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
